--- a/output/pdf_financials_xlsx/BEM.xlsx
+++ b/output/pdf_financials_xlsx/BEM.xlsx
@@ -7799,16 +7799,16 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.588607</v>
+        <v>0.511566</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>2.368056</v>
+        <v>2.305613</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.015001</v>
+        <v>-0.014499</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.015226</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -44170,7 +44170,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -45960,7 +45964,11 @@
           <t>Recovery of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BEM.xlsx
+++ b/output/pdf_financials_xlsx/BEM.xlsx
@@ -951,46 +951,46 @@
         <v>0.196937</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.174993</v>
+        <v>0.265906</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.13256</v>
+        <v>1.766262</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.134189</v>
+        <v>0.155722</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.128404</v>
+        <v>0.165767</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.316106</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.308455</v>
+        <v>0.446735</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.304808</v>
+        <v>0.537279</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.393225</v>
+        <v>0.768169</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.307289</v>
+        <v>0.85728</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.427143</v>
+        <v>1.839113</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.38559</v>
+        <v>1.032141</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.426797</v>
+        <v>1.744428</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.477423</v>
+        <v>1.751558</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.366607</v>
+        <v>1.218003</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0.322399</v>
@@ -1012,13 +1012,13 @@
         <v>-0.196351</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.174516</v>
+        <v>-0.265429</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.09560200000000001</v>
+        <v>-1.729304</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.088932</v>
+        <v>-0.110465</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.17069</v>
@@ -1036,19 +1036,19 @@
         <v>-0.774618</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.307289</v>
+        <v>-0.85728</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.427143</v>
+        <v>-1.839113</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.38559</v>
+        <v>-1.032141</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.426797</v>
+        <v>-1.744428</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.477423</v>
+        <v>-1.751558</v>
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003819</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000266</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00074</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>-0.699072</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.546864</v>
+        <v>-2.550683</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.285886</v>
@@ -2114,10 +2114,10 @@
         <v>-0.480909</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.536763</v>
+        <v>-0.537029</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.421552</v>
+        <v>-1.422292</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.865862</v>
@@ -2227,7 +2227,7 @@
         <v>-0.699072</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.546864</v>
+        <v>-2.550683</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.285886</v>
@@ -2236,10 +2236,10 @@
         <v>-0.480909</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.536763</v>
+        <v>-0.537029</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.421552</v>
+        <v>-1.422292</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.865862</v>
@@ -2530,13 +2530,13 @@
         <v>0.000841</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.107337</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.069647</v>
@@ -2545,28 +2545,28 @@
         <v>0.001773</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000279</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.002414</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.247754</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.023241</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.065732</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001449</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.002755</v>
       </c>
     </row>
     <row r="35">
@@ -2652,13 +2652,13 @@
         <v>0.000841</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.117337</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.001508</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.071397</v>
@@ -2667,28 +2667,28 @@
         <v>0.008773</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.002083</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.001779</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.009913999999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.252754</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.025241</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.001</v>
+        <v>0.066732</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.003949</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.004</v>
+        <v>0.006755</v>
       </c>
     </row>
     <row r="37">
@@ -3384,13 +3384,13 @@
         <v>0.011927</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>8.1e-05</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.107337</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8e-06</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3399,28 +3399,28 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.000583</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.034279</v>
+        <v>0.034</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.011217</v>
+        <v>0.008803</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.422754</v>
+        <v>0.175</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.110741</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.226398</v>
+        <v>0.160666</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.018946</v>
+        <v>0.017497</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.012755</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="49">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -53744,7 +53744,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -55670,7 +55670,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -55878,7 +55878,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -55952,10 +55952,10 @@
         </is>
       </c>
       <c r="S447" s="5" t="n">
-        <v>-1.751558</v>
+        <v>1.751558</v>
       </c>
       <c r="T447" s="5" t="n">
-        <v>-1.218003</v>
+        <v>1.218003</v>
       </c>
       <c r="U447" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -56852,10 +56852,10 @@
         </is>
       </c>
       <c r="I456" s="5" t="n">
-        <v>-0.155722</v>
+        <v>0.155722</v>
       </c>
       <c r="J456" s="5" t="n">
-        <v>-0.165767</v>
+        <v>0.165767</v>
       </c>
       <c r="K456" t="inlineStr">
         <is>
@@ -56883,10 +56883,10 @@
         <v>1.032141</v>
       </c>
       <c r="R456" s="5" t="n">
-        <v>-1.744428</v>
+        <v>1.744428</v>
       </c>
       <c r="S456" s="5" t="n">
-        <v>-1.751558</v>
+        <v>1.751558</v>
       </c>
       <c r="T456" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -57938,10 +57938,10 @@
         </is>
       </c>
       <c r="Q466" s="5" t="n">
-        <v>-1.032141</v>
+        <v>1.032141</v>
       </c>
       <c r="R466" s="5" t="n">
-        <v>-1.744428</v>
+        <v>1.744428</v>
       </c>
       <c r="S466" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -59780,7 +59780,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -60626,7 +60626,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -60732,7 +60732,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -62522,7 +62522,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -62632,7 +62632,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -62671,10 +62671,10 @@
         </is>
       </c>
       <c r="L511" s="5" t="n">
-        <v>-0.446735</v>
+        <v>0.446735</v>
       </c>
       <c r="M511" s="5" t="n">
-        <v>-0.537279</v>
+        <v>0.537279</v>
       </c>
       <c r="N511" t="inlineStr">
         <is>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -68748,7 +68748,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">

--- a/output/pdf_financials_xlsx/BEM.xlsx
+++ b/output/pdf_financials_xlsx/BEM.xlsx
@@ -6706,22 +6706,22 @@
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013185</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.033203</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012375</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.021705</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.017165</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.018336</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>0</v>
@@ -7023,22 +7023,22 @@
         <v>-0.03241</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.006229</v>
+        <v>-0.019414</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.020269</v>
+        <v>0.053472</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.204666</v>
+        <v>0.192291</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.255077</v>
+        <v>0.233372</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.413652</v>
+        <v>0.430817</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.746241</v>
+        <v>0.764577</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0.394729</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.148139</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.10863</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>0</v>
@@ -34096,7 +34096,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -41456,7 +41460,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -42600,7 +42608,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -43966,7 +43978,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -48930,7 +48946,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
